--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,56 +680,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133349362</v>
+        <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>57896</v>
+        <v>92327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100001</v>
+        <v>3008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Berget Väst, Hl</t>
+          <t>Hyggeskant väster Mattjärn, Hyggeskant väster Mattjärn, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>334899</v>
+        <v>334663</v>
       </c>
       <c r="R2" t="n">
-        <v>6386850</v>
+        <v>6386702</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,17 +748,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>20/4 - 29/4 upptäckter 8 (15)</t>
+          <t>Currydoftande, kryddigt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,13 +777,9 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -788,39 +789,39 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Mats Foss</t>
+          <t>Mats Foss, Steve Daurer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133349362</t>
+          <t>https://artportalen.se/Sighting/136920062</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133350119</v>
+        <v>133349362</v>
       </c>
       <c r="B3" t="n">
-        <v>57972</v>
+        <v>57896</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -883,7 +884,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1/5 upptäckter 1 (2)</t>
+          <t>20/4 - 29/4 upptäckter 8 (15)</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,16 +915,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133350119</t>
+          <t>https://artportalen.se/Sighting/133349362</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133350526</v>
+        <v>133350119</v>
       </c>
       <c r="B4" t="n">
-        <v>57162</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -931,21 +932,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1003,7 +1004,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>25/4 - 5/5 upptäckter 29 (74)</t>
+          <t>1/5 upptäckter 1 (2)</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,38 +1035,38 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133350526</t>
+          <t>https://artportalen.se/Sighting/133350119</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133349574</v>
+        <v>133350526</v>
       </c>
       <c r="B5" t="n">
-        <v>58519</v>
+        <v>57162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102990</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1123,7 +1124,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>30/4 uppräckter 1 (2)</t>
+          <t>25/4 - 5/5 upptäckter 29 (74)</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,33 +1155,33 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133349574</t>
+          <t>https://artportalen.se/Sighting/133350526</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133349748</v>
+        <v>133349574</v>
       </c>
       <c r="B6" t="n">
-        <v>58349</v>
+        <v>58519</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1243,7 +1244,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>21/4 - 6/5</t>
+          <t>30/4 uppräckter 1 (2)</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,38 +1275,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133349748</t>
+          <t>https://artportalen.se/Sighting/133349574</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133350419</v>
+        <v>133349748</v>
       </c>
       <c r="B7" t="n">
-        <v>58136</v>
+        <v>58349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1363,7 +1364,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>upptäckter (2)</t>
+          <t>21/4 - 6/5</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,38 +1395,38 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133350419</t>
+          <t>https://artportalen.se/Sighting/133349748</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133350567</v>
+        <v>133350419</v>
       </c>
       <c r="B8" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1483,7 +1484,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>22/4 - 6/5 upptäckter 33 (470)</t>
+          <t>upptäckter (2)</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,16 +1515,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133350567</t>
+          <t>https://artportalen.se/Sighting/133350419</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133349200</v>
+        <v>133350567</v>
       </c>
       <c r="B9" t="n">
-        <v>58596</v>
+        <v>58131</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,21 +1532,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103041</v>
+        <v>103023</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bergfink</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fringilla montifringilla</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1603,7 +1604,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>22/4 - 29/4 upptäckter 7 (7)</t>
+          <t>22/4 - 6/5 upptäckter 33 (470)</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1634,16 +1635,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133349200</t>
+          <t>https://artportalen.se/Sighting/133350567</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133349484</v>
+        <v>133349200</v>
       </c>
       <c r="B10" t="n">
-        <v>58658</v>
+        <v>58596</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,21 +1652,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103044</v>
+        <v>103041</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1723,7 +1724,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>21/4 - 6/5 upptäckter 375 (689)</t>
+          <t>22/4 - 29/4 upptäckter 7 (7)</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1753,6 +1754,126 @@
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133349200</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133349484</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Berget Väst, Hl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>334899</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6386850</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mölndal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lindome</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>21/4 - 6/5 upptäckter 375 (689)</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mats Foss</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Via Mats Foss</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/133349484</t>
         </is>
@@ -1769,6 +1890,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92327</v>
+        <v>92329</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92329</v>
+        <v>92331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92331</v>
+        <v>92332</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92332</v>
+        <v>92338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92338</v>
+        <v>92342</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92342</v>
+        <v>92344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92344</v>
+        <v>92357</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92359</v>
+        <v>92362</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92362</v>
+        <v>92372</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92376</v>
+        <v>92378</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92378</v>
+        <v>92383</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92383</v>
+        <v>92395</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92395</v>
+        <v>92396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92396</v>
+        <v>92399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92399</v>
+        <v>92400</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92400</v>
+        <v>92403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
